--- a/Apex 데이터 테이블 명세서.xlsx
+++ b/Apex 데이터 테이블 명세서.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\{ 프로젝트 기반 풀스택 개발자 양성 과정 }\A조 Apex\gamepex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F37344C-5349-44DE-8277-73B92CB6650A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3569AF1-665B-432A-A1A1-28F2C1150430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{AC449A03-C93A-4853-895D-61D8656DAC6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{AC449A03-C93A-4853-895D-61D8656DAC6C}"/>
   </bookViews>
   <sheets>
     <sheet name="관리자" sheetId="1" r:id="rId1"/>
     <sheet name="사용자" sheetId="5" r:id="rId2"/>
     <sheet name="게임기" sheetId="4" r:id="rId3"/>
-    <sheet name="게임 타이틀" sheetId="19" r:id="rId4"/>
-    <sheet name="주문목록" sheetId="24" r:id="rId5"/>
-    <sheet name="주문" sheetId="9" r:id="rId6"/>
+    <sheet name="게임타이틀" sheetId="19" r:id="rId4"/>
+    <sheet name="렌탈목록" sheetId="24" r:id="rId5"/>
+    <sheet name="렌탈" sheetId="9" r:id="rId6"/>
     <sheet name="요청" sheetId="10" r:id="rId7"/>
     <sheet name="우편번호" sheetId="7" r:id="rId8"/>
     <sheet name="후기" sheetId="12" r:id="rId9"/>
@@ -27,13 +27,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">QNA!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'게임 타이틀'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">게임기!$A$2:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">게임기!$A$2:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">게임타이틀!$A$2:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">공지사항!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">관리자!$A$2:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">사용자!$A$2:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">우편번호!$A$2:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">주문!$A$2:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">관리자!$A$2:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">렌탈!$A$2:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">사용자!$A$2:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">우편번호!$A$2:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">후기!$A$2:$G$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="287">
   <si>
     <t>Column</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -93,10 +93,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>직원 비밀번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>O</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -142,9 +138,6 @@
   </si>
   <si>
     <t>varchar(50)</t>
-  </si>
-  <si>
-    <t>varchar(50)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -159,10 +152,6 @@
     <t>char(13)</t>
   </si>
   <si>
-    <t>직원 전화번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -187,14 +176,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>) comment '관리자 테이블';</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>) comment '사용자 테이블';</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>관리자 테이블(tbl_staff)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -203,10 +184,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>varchar(50)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>varchar(20)</t>
   </si>
   <si>
@@ -217,17 +194,6 @@
     <t>varchar(30)</t>
   </si>
   <si>
-    <t>대여기간(최소 3일)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>foreign key (staff_id) references tbl_staff (staff_id)</t>
-  </si>
-  <si>
-    <t>성별(m, w, n)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>생년월일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -281,10 +247,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>) comment '우편번호 테이블';</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mb_id</t>
   </si>
   <si>
@@ -315,9 +277,6 @@
     <t>mb_moddate</t>
   </si>
   <si>
-    <t>unique (mb_nickname)</t>
-  </si>
-  <si>
     <t>회원 테이블(tbl_member)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -338,26 +297,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>date</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>대여 시작일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대여 종료일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>반납일(관리자)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>&gt;&gt; AddressDTO.java</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -376,15 +319,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상품 사양</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품 이름</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mb_no</t>
+    <t>tinyint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>staff_state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>staff_no</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -392,42 +339,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tinyint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>char(5)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>staff_state</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>staff_no</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>O</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>unique (staff_id)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>char(60)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>unique(mb_id)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>staff_birth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -449,11 +368,6 @@
   </si>
   <si>
     <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>직원 상태
-(0:미승인, 1:재직, 2:휴직 3:퇴직)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -505,36 +419,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제주 3,000원, 제주 외 도서 산간 5,000원 추가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대여가능여부
-(0:대여가능 1:대여중 2:입고대기)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>회원 등급</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주문한 회원 아이디</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>상품 고유 번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문 발생 날짜 및 시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문 총액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메일 주소(중복 불가)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -556,31 +445,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>배송비(0:일반3000원 1:무료 2:특수5000원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>회원여부(상태)
-(0:회원, 1:휴면회원, 2:탈퇴회원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수령자 전화번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수령지 주소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수령지 우편번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수령자 (회원 정보와 동일) 버튼 만들기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mb_addr</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -589,10 +453,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>송장번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -601,13 +461,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>foreign key (mb_id) references tbl_member (mb_id)</t>
-  </si>
-  <si>
-    <t>상품별 구매 수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>후기 테이블(tbl_review)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -646,15 +499,6 @@
   </si>
   <si>
     <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>요청 번호(자동증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입고여부
-(0:미입고 1:입고완료 2:입고 대기중)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -926,17 +770,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주문 상태 (0:pending 1:shipped 2:cancelled 3:reject)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">varchar(50) </t>
-  </si>
-  <si>
     <t>con_name</t>
   </si>
   <si>
@@ -952,38 +789,12 @@
     <t>con_content</t>
   </si>
   <si>
-    <t>con_status</t>
-  </si>
-  <si>
     <t>con_regdate</t>
   </si>
   <si>
     <t>con_moddate</t>
   </si>
   <si>
-    <t>primary key (con_no),</t>
-  </si>
-  <si>
-    <t>unique (con_serial)</t>
-  </si>
-  <si>
-    <t>대여 가격</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대여 가능 여부
-(0:대여가능 1:대여중 2:입고대기)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>con_no</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>단말기 일련 번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>varchar(255)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1000,10 +811,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게임기 번호(자동증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>썸네일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1016,9 +823,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ttl_no</t>
-  </si>
-  <si>
     <t>ttl_name</t>
   </si>
   <si>
@@ -1034,54 +838,12 @@
     <t>ttl_content</t>
   </si>
   <si>
-    <t>ttl_status</t>
-  </si>
-  <si>
     <t>ttl_regdate</t>
   </si>
   <si>
     <t>ttl_moddate</t>
   </si>
   <si>
-    <t>primary key (ttl_no),</t>
-  </si>
-  <si>
-    <t>unique (ttl_serial)</t>
-  </si>
-  <si>
-    <t>게임 타이틀 테이블(tbl_title)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>직원 번호(자동증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 타이틀 번호(자동증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>열1</t>
-  </si>
-  <si>
-    <t>열2</t>
-  </si>
-  <si>
-    <t>열3</t>
-  </si>
-  <si>
-    <t>열4</t>
-  </si>
-  <si>
-    <t>열5</t>
-  </si>
-  <si>
-    <t>열6</t>
-  </si>
-  <si>
-    <t>열7</t>
-  </si>
-  <si>
     <t>타이틀명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1090,10 +852,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게임 장르</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ttl_platform</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1106,48 +864,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>회원 번호(자동증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>회원 아이디 (중복불가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>닉네임(중복불가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전화번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>우편번호 (검색하기)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>주소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rt_name</t>
-  </si>
-  <si>
-    <t>rt_phone</t>
-  </si>
-  <si>
-    <t>rt_zipcode</t>
-  </si>
-  <si>
-    <t>rt_addr</t>
-  </si>
-  <si>
-    <t>rt_quantity</t>
-  </si>
-  <si>
-    <t>rt_rentdays</t>
-  </si>
-  <si>
     <t>rt_amount</t>
   </si>
   <si>
@@ -1157,12 +877,6 @@
     <t>rt_invoice</t>
   </si>
   <si>
-    <t>rt_delivery</t>
-  </si>
-  <si>
-    <t>rt_status</t>
-  </si>
-  <si>
     <t>rt_startdate</t>
   </si>
   <si>
@@ -1172,99 +886,300 @@
     <t>rt_regdate</t>
   </si>
   <si>
-    <t>주문 번호(자동증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>req_no</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>req_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>req_spec</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>req_maker</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>req_status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>req_regdate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>req_moddate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>요청 테이블(tbl_con_request)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>) comment '요청 테이블';</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문 결제 방식(1:현금 2:카드 3:페이)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>) comment '게임기 테이블';</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>) comment '타이틀 테이블';</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>) comment '대여 테이블';</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rt_rtndate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>con_amount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ttl_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문 테이블(tbl_oredr)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>item_no</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>order_no</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>item_type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주문상품 테이블(tbl_oredr_item)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문상품 번호(자동증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ttl_no</t>
+    <t>기본키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본키, 자동증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사원번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본값:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고유키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">고유키, 최고 관리자 부여
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(개인 수정 불가)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m,w,n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연락처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:회원(기본값), 1:휴면회원, 2:탈퇴회원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:미승인(기본값), 1:재직, 2:휴직, 3:퇴직</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>닉네임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검색하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:대여가능(기본값) 1:대여중 2:입고대기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일련번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원 아이디</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외래키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">varchar(20) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>con_state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임타이틀 테이블(tbl_title)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청 번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청 테이블(tbl_wish)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wish_no</t>
+  </si>
+  <si>
+    <t>wish_name</t>
+  </si>
+  <si>
+    <t>wish_status</t>
+  </si>
+  <si>
+    <t>wish_regdate</t>
+  </si>
+  <si>
+    <t>wish_moddate</t>
+  </si>
+  <si>
+    <t>상품명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wish_platform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:미입고 1:입고대기 2:입고완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wish_content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>렌탈 테이블(tbl_rental)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt_no</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wish_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임기, 타이틀, 액세서리 등..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임기/타이틀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_quantity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_regdate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_moddate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>렌탈번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>렌탈상세 테이블(tbl_item)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최저값:3 (check 제약조건)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt_state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종료일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반납일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배송비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt_days</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:pending(기본값) 1:shipped 2:cancelled 3:rejected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대여일수(최소 3일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:카드 1:현금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt_shipfee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제총액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 1일 대여료 총합 X 대여일수 + 배송비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자 권한</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1438,15 +1353,6 @@
       <top style="thin">
         <color theme="0" tint="-0.34998626667073579"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
       <bottom style="thin">
         <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
@@ -1609,6 +1515,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1618,7 +1535,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1688,238 +1605,182 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="96">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
+  <dxfs count="76">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
         <top style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </top>
         <bottom style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </bottom>
-        <vertical/>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </left>
@@ -1932,284 +1793,28 @@
         <bottom style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
+        <right/>
         <top style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </top>
         <bottom style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
+      <border outline="0">
         <right style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2781,6 +2386,18 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
@@ -2804,73 +2421,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
@@ -3053,73 +2603,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -3176,24 +2659,99 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3216,61 +2774,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
@@ -3384,59 +2887,16 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
@@ -3554,15 +3014,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>28577</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>110853</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3599,15 +3059,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>428663</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3644,16 +3104,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>361949</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>95249</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>638174</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>191338</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>96089</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3689,16 +3149,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>371474</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>647699</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>143713</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>96089</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3734,16 +3194,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>643659</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>27288</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>74913</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3781,22 +3241,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{58F03EDD-8555-43F1-B2E7-944B4086B6D4}" name="표4" displayName="표4" ref="A2:G17" totalsRowShown="0" headerRowDxfId="95" headerRowBorderDxfId="94" tableBorderDxfId="93" totalsRowBorderDxfId="92">
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{DE7AF2E1-2E34-4F6F-89FB-AED156E93F2C}" name="Column" dataDxfId="91"/>
-    <tableColumn id="2" xr3:uid="{3A1EC3CB-638E-4921-BC0D-B6DA479F4CB2}" name="Data Type" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{615D6A3E-796D-42CC-A6C2-369645BC4E73}" name="Default" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{002DFA58-CB0E-48D4-ABC9-3517D8694680}" name="PK" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{AB321166-E3EC-4159-8622-DDD35503632F}" name="NN" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{70CAB3B6-AEAA-4D52-95D2-49E38250BDC7}" name="Comment"/>
-    <tableColumn id="7" xr3:uid="{552E6029-4B31-4BA5-B3FF-5016F78199AC}" name="비고" dataDxfId="86"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{58F03EDD-8555-43F1-B2E7-944B4086B6D4}" name="표4" displayName="표4" ref="A2:E15" totalsRowShown="0" headerRowDxfId="75" headerRowBorderDxfId="74" tableBorderDxfId="73" totalsRowBorderDxfId="72">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{DE7AF2E1-2E34-4F6F-89FB-AED156E93F2C}" name="Column" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{3A1EC3CB-638E-4921-BC0D-B6DA479F4CB2}" name="Data Type" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{AB321166-E3EC-4159-8622-DDD35503632F}" name="NN" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{70CAB3B6-AEAA-4D52-95D2-49E38250BDC7}" name="Comment" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{552E6029-4B31-4BA5-B3FF-5016F78199AC}" name="비고" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CA4E76DE-4C6B-4B99-89C2-63BC62647519}" name="표1" displayName="표1" ref="A2:H16" totalsRowShown="0" headerRowDxfId="47" tableBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CA4E76DE-4C6B-4B99-89C2-63BC62647519}" name="표1" displayName="표1" ref="A2:H16" totalsRowShown="0" headerRowDxfId="33" tableBorderDxfId="32">
   <autoFilter ref="A2:H16" xr:uid="{CA4E76DE-4C6B-4B99-89C2-63BC62647519}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3808,21 +3266,21 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{8C9D0E22-ADCA-4540-9688-23547679B6C8}" name="Column" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{FA66E30E-D4C5-4113-ACC4-BE8B6DB19033}" name="Data Type" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{6922D11B-CC97-456B-A886-9CEC74D25E14}" name="Default" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{5CA6E294-2B3C-47D4-B18C-20BB67E1D99B}" name="PK" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{2BA5941E-8F52-48A2-8DFA-E58422140A49}" name="FK" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{DBFCAC99-5D4D-4CBF-8207-42DA651427BD}" name="NN" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{EEA72C2B-4C87-4857-B38C-038CD7B554DF}" name="Comment" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{24F7E852-CD00-40AB-949B-E8612E19083F}" name="비고" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{8C9D0E22-ADCA-4540-9688-23547679B6C8}" name="Column" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{FA66E30E-D4C5-4113-ACC4-BE8B6DB19033}" name="Data Type" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{6922D11B-CC97-456B-A886-9CEC74D25E14}" name="Default" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{5CA6E294-2B3C-47D4-B18C-20BB67E1D99B}" name="PK" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{2BA5941E-8F52-48A2-8DFA-E58422140A49}" name="FK" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{DBFCAC99-5D4D-4CBF-8207-42DA651427BD}" name="NN" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{EEA72C2B-4C87-4857-B38C-038CD7B554DF}" name="Comment" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{24F7E852-CD00-40AB-949B-E8612E19083F}" name="비고" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{39C81166-FA7E-4075-A160-CC85D603AF54}" name="표1_3" displayName="표1_3" ref="A2:H12" totalsRowShown="0" headerRowDxfId="37" tableBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{39C81166-FA7E-4075-A160-CC85D603AF54}" name="표1_3" displayName="표1_3" ref="A2:H12" totalsRowShown="0" headerRowDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="A2:H12" xr:uid="{CA4E76DE-4C6B-4B99-89C2-63BC62647519}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3834,21 +3292,21 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{B108C0C8-1CD1-4355-93B2-E1314768407B}" name="Column" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{29F49743-BD31-4DB4-ACF6-43B764681223}" name="Data Type" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{63B27C6D-BD53-4006-8243-8ADEB46F5151}" name="Default" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{8DC66295-E0E7-420F-85D1-65F305BCED5D}" name="PK" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{729F02E6-1C9F-431D-8093-532DB44BC686}" name="FK" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{F985BD69-5F60-401C-9B48-68A4C6C0E506}" name="NN" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{E5AB7063-93F9-473E-A036-CC9E19A3ABB3}" name="Comment" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{A0C7C71C-DF77-4F52-A14D-8332718AA59D}" name="비고" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{B108C0C8-1CD1-4355-93B2-E1314768407B}" name="Column" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{29F49743-BD31-4DB4-ACF6-43B764681223}" name="Data Type" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{63B27C6D-BD53-4006-8243-8ADEB46F5151}" name="Default" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{8DC66295-E0E7-420F-85D1-65F305BCED5D}" name="PK" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{729F02E6-1C9F-431D-8093-532DB44BC686}" name="FK" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{F985BD69-5F60-401C-9B48-68A4C6C0E506}" name="NN" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{E5AB7063-93F9-473E-A036-CC9E19A3ABB3}" name="Comment" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{A0C7C71C-DF77-4F52-A14D-8332718AA59D}" name="비고" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5E64E0FE-5E09-4404-AF69-AFA46D685BEE}" name="표1_34" displayName="표1_34" ref="A2:H17" totalsRowShown="0" headerRowDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5E64E0FE-5E09-4404-AF69-AFA46D685BEE}" name="표1_34" displayName="표1_34" ref="A2:H17" totalsRowShown="0" headerRowDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:H17" xr:uid="{CA4E76DE-4C6B-4B99-89C2-63BC62647519}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3860,36 +3318,32 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{8936DEB8-7D4B-44C2-ACF8-3AAD127B9537}" name="Column" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{64E1C0E5-EFB3-45E2-B9E6-428473990808}" name="Data Type" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{E49FA7C8-66BA-4CA6-B9FE-68090FEE7476}" name="Default" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{89FA2802-0597-4ACA-B140-7A02B2F17BD7}" name="PK" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{E30151BB-F952-4E2A-B0BC-3FDB99441FFD}" name="FK" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{3A0F67FB-EE53-4561-B88B-2218A0F5605D}" name="NN" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{387E1428-54B9-47C7-B179-6B64C84CA356}" name="Comment" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{8AC11FDB-2559-4000-A830-2D029808ECDB}" name="비고" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{8936DEB8-7D4B-44C2-ACF8-3AAD127B9537}" name="Column" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{64E1C0E5-EFB3-45E2-B9E6-428473990808}" name="Data Type" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{E49FA7C8-66BA-4CA6-B9FE-68090FEE7476}" name="Default" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{89FA2802-0597-4ACA-B140-7A02B2F17BD7}" name="PK" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{E30151BB-F952-4E2A-B0BC-3FDB99441FFD}" name="FK" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{3A0F67FB-EE53-4561-B88B-2218A0F5605D}" name="NN" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{387E1428-54B9-47C7-B179-6B64C84CA356}" name="Comment" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{8AC11FDB-2559-4000-A830-2D029808ECDB}" name="비고" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{3BBD5688-D5C9-452A-973C-03F8D977E9EA}" name="표10" displayName="표10" ref="A2:G16" totalsRowShown="0" headerRowDxfId="74">
-  <autoFilter ref="A2:G16" xr:uid="{3BBD5688-D5C9-452A-973C-03F8D977E9EA}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{3BBD5688-D5C9-452A-973C-03F8D977E9EA}" name="표10" displayName="표10" ref="A2:E15" totalsRowShown="0" headerRowDxfId="68">
+  <autoFilter ref="A2:E15" xr:uid="{3BBD5688-D5C9-452A-973C-03F8D977E9EA}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
     <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="7">
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A5066565-8C8E-42EB-AD35-FE243EE49754}" name="Column"/>
-    <tableColumn id="2" xr3:uid="{8BBE96FB-BC3C-4B90-A23C-9403BC4D7BC8}" name="Data Type" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{F2FF3729-5208-4707-A5F5-B12C60A324E5}" name="Default"/>
-    <tableColumn id="4" xr3:uid="{701B62C1-4AC4-485C-8823-A9F8FF51A0D7}" name="PK"/>
-    <tableColumn id="5" xr3:uid="{EC102AAF-E5BF-4246-BC74-E2866194FB7F}" name="NN" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{8BBE96FB-BC3C-4B90-A23C-9403BC4D7BC8}" name="Data Type" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{EC102AAF-E5BF-4246-BC74-E2866194FB7F}" name="NN" dataDxfId="66"/>
     <tableColumn id="6" xr3:uid="{63082956-2889-4143-BC8C-3B0833AEB8B8}" name="Comment"/>
     <tableColumn id="7" xr3:uid="{AA8108A5-9FA5-4680-9CBF-15A155069BD5}" name="비고"/>
   </tableColumns>
@@ -3898,148 +3352,111 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{76CED7F7-B3E0-45B5-A9DF-C0ECE40B2BAC}" name="표11" displayName="표11" ref="A2:O14" totalsRowShown="0" headerRowDxfId="85" headerRowBorderDxfId="84" tableBorderDxfId="83">
-  <autoFilter ref="A2:O14" xr:uid="{76CED7F7-B3E0-45B5-A9DF-C0ECE40B2BAC}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{76CED7F7-B3E0-45B5-A9DF-C0ECE40B2BAC}" name="표11" displayName="표11" ref="A2:E12" totalsRowShown="0" headerRowDxfId="65" headerRowBorderDxfId="64" tableBorderDxfId="63">
+  <autoFilter ref="A2:E12" xr:uid="{76CED7F7-B3E0-45B5-A9DF-C0ECE40B2BAC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
     <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-    <filterColumn colId="12" hiddenButton="1"/>
-    <filterColumn colId="13" hiddenButton="1"/>
-    <filterColumn colId="14" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{5CFD47E5-13F4-4A5A-B957-CF4E15B6771A}" name="Column" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{DE3B7FF6-7BA5-4C0F-89BB-17711372BE5E}" name="Data Type" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{D223A70E-564F-4CF0-800A-32CB66F3D78E}" name="Default" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{9AF594F3-2666-49FC-A51F-E26EABABE027}" name="PK" dataDxfId="79"/>
-    <tableColumn id="5" xr3:uid="{FC9D85B4-6194-4DEE-BD3B-EE89E253C253}" name="FK" dataDxfId="78"/>
-    <tableColumn id="6" xr3:uid="{60FB7AD1-F8AA-4D0A-96CA-72FC386AC5FA}" name="NN" dataDxfId="77"/>
-    <tableColumn id="7" xr3:uid="{08FB6E6F-A31C-457B-BCAB-5D8CED635959}" name="Comment" dataDxfId="76"/>
-    <tableColumn id="8" xr3:uid="{86D3B2AE-C007-453D-9EA0-61E958621F78}" name="비고" dataDxfId="75"/>
-    <tableColumn id="9" xr3:uid="{FB4B765C-C252-45CA-B56C-EBCC10490853}" name="열1" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{8540BFDB-DDCB-472A-8DC9-7F50F3599DA5}" name="열2" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{43D7EF09-0806-4CF7-8706-76034710988A}" name="열3" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{9D97548A-B648-4E43-9994-0C17979D50B6}" name="열4" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{18AA288F-0CFD-41DF-A008-8730DE04A484}" name="열5" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{83986FB4-8F45-4EC5-8094-5866EF001554}" name="열6" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{B5345020-9D31-4293-9AEE-91B0583F189C}" name="열7" dataDxfId="11"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{5CFD47E5-13F4-4A5A-B957-CF4E15B6771A}" name="Column" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{DE3B7FF6-7BA5-4C0F-89BB-17711372BE5E}" name="Data Type" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{60FB7AD1-F8AA-4D0A-96CA-72FC386AC5FA}" name="NN" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{08FB6E6F-A31C-457B-BCAB-5D8CED635959}" name="Comment" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{86D3B2AE-C007-453D-9EA0-61E958621F78}" name="비고" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{69DAC7DF-21EF-400A-BBE2-907A05891D9A}" name="표7_6" displayName="표7_6" ref="A2:G19" totalsRowShown="0" headerRowDxfId="10">
-  <autoFilter ref="A2:G19" xr:uid="{69DAC7DF-21EF-400A-BBE2-907A05891D9A}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FB63C8E4-B436-4899-8786-CB6BF9A371D1}" name="Column" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{707188D2-6EC4-4873-8AC1-6D45BC6567A2}" name="Data Type" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{2FF3277F-8FEA-43AC-A0BB-37602806B369}" name="Default" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{ECFB7C50-5E0D-4C26-B33D-98085F3B71D5}" name="PK" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{CC88D3B5-EA50-4881-806D-60F976C3F2D9}" name="FK" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{1052DC46-1508-4357-8B9F-FD5909BB6B76}" name="NN" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{9417BE86-47B2-4672-9857-6F9913EC9394}" name="Comment" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{69DAC7DF-21EF-400A-BBE2-907A05891D9A}" name="표7_6" displayName="표7_6" ref="A2:D10" totalsRowShown="0" headerRowDxfId="57">
+  <autoFilter ref="A2:D10" xr:uid="{69DAC7DF-21EF-400A-BBE2-907A05891D9A}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{FB63C8E4-B436-4899-8786-CB6BF9A371D1}" name="Column" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{707188D2-6EC4-4873-8AC1-6D45BC6567A2}" name="Data Type" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{1052DC46-1508-4357-8B9F-FD5909BB6B76}" name="NN" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{9417BE86-47B2-4672-9857-6F9913EC9394}" name="Comment" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7A5662C3-BAE4-4E1C-A58C-B1748CA6F7D6}" name="표8_7" displayName="표8_7" ref="H2:H3" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
-  <autoFilter ref="H2:H3" xr:uid="{7A5662C3-BAE4-4E1C-A58C-B1748CA6F7D6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7A5662C3-BAE4-4E1C-A58C-B1748CA6F7D6}" name="표8_7" displayName="표8_7" ref="E2:E6" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+  <autoFilter ref="E2:E6" xr:uid="{7A5662C3-BAE4-4E1C-A58C-B1748CA6F7D6}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8797FEE5-6E06-4518-A00A-86C1850904DF}" name="비고" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8797FEE5-6E06-4518-A00A-86C1850904DF}" name="비고" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C2ABAEA9-46EA-4BCA-81D8-71E1412943BE}" name="표7" displayName="표7" ref="A2:G28" totalsRowShown="0" headerRowDxfId="67">
-  <autoFilter ref="A2:G28" xr:uid="{C2ABAEA9-46EA-4BCA-81D8-71E1412943BE}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C2ABAEA9-46EA-4BCA-81D8-71E1412943BE}" name="표7" displayName="표7" ref="A2:D15" totalsRowShown="0" headerRowDxfId="51">
+  <autoFilter ref="A2:D15" xr:uid="{C2ABAEA9-46EA-4BCA-81D8-71E1412943BE}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{3A906EC9-8141-48AE-BF34-F27C3BE54E6B}" name="Column" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{E4F5A37B-F3AD-4885-8BDC-FF1F347F7EA4}" name="Data Type" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{77DAB525-B739-4F13-8D7C-2BF484206F97}" name="Default" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{ACC20950-B948-4FAE-9F28-CC6F88AB0960}" name="PK" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{2DD11EC7-E46D-4F42-BD61-C3F65C68D813}" name="FK" dataDxfId="62"/>
-    <tableColumn id="6" xr3:uid="{3846511B-9582-48CE-AE72-215C51E1D8D2}" name="NN" dataDxfId="61"/>
-    <tableColumn id="7" xr3:uid="{C474A123-EE62-4FD5-A1F9-1FB4A44447AD}" name="Comment" dataDxfId="60"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{3A906EC9-8141-48AE-BF34-F27C3BE54E6B}" name="Column" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{E4F5A37B-F3AD-4885-8BDC-FF1F347F7EA4}" name="Data Type" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{3846511B-9582-48CE-AE72-215C51E1D8D2}" name="NN" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{C474A123-EE62-4FD5-A1F9-1FB4A44447AD}" name="Comment" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{09810E88-EBAD-4FF0-8E63-B89D65E1F24B}" name="표8" displayName="표8" ref="H2:H3" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
-  <autoFilter ref="H2:H3" xr:uid="{09810E88-EBAD-4FF0-8E63-B89D65E1F24B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{09810E88-EBAD-4FF0-8E63-B89D65E1F24B}" name="표8" displayName="표8" ref="E2:E7" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+  <autoFilter ref="E2:E7" xr:uid="{09810E88-EBAD-4FF0-8E63-B89D65E1F24B}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{C292FE39-034C-4C17-A8AF-EDFCA6945F49}" name="비고" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{C292FE39-034C-4C17-A8AF-EDFCA6945F49}" name="비고" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0A4AD4E9-F101-4638-B649-459BAD6CAF0F}" name="표9" displayName="표9" ref="A2:H10" totalsRowShown="0" headerRowDxfId="56">
-  <autoFilter ref="A2:H10" xr:uid="{0A4AD4E9-F101-4638-B649-459BAD6CAF0F}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0A4AD4E9-F101-4638-B649-459BAD6CAF0F}" name="표9" displayName="표9" ref="A2:E11" totalsRowShown="0" headerRowDxfId="43">
+  <autoFilter ref="A2:E11" xr:uid="{0A4AD4E9-F101-4638-B649-459BAD6CAF0F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
     <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F61BD124-B870-4E43-A049-DD45653C5989}" name="Column" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{BFBA2E1E-7A4A-4315-B10E-A0E067657AED}" name="Data Type" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{AE59F2F7-7F9E-4B83-9E24-A95CA17E51F1}" name="Default" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{ECDDCDE8-7541-489D-9D93-0D3A3236DF23}" name="PK" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{0B6BA73E-2663-4BCE-A9BE-003DCA0AB202}" name="FK" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{1927EF84-03F7-456B-AC05-6CF068C3D16B}" name="NN" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{FD253E0A-09D4-44A5-8EDA-0943FBD70E14}" name="Comment" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{35D36DE9-0322-4674-8F88-8A503161C008}" name="비고" dataDxfId="48"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{F61BD124-B870-4E43-A049-DD45653C5989}" name="Column" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{BFBA2E1E-7A4A-4315-B10E-A0E067657AED}" name="Data Type" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{1927EF84-03F7-456B-AC05-6CF068C3D16B}" name="NN" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{FD253E0A-09D4-44A5-8EDA-0943FBD70E14}" name="Comment" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{35D36DE9-0322-4674-8F88-8A503161C008}" name="비고" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C6AD608D-93C8-4212-8CE5-4CD51EEA574F}" name="표12" displayName="표12" ref="A2:F8" totalsRowShown="0" headerRowDxfId="71">
-  <autoFilter ref="A2:F8" xr:uid="{C6AD608D-93C8-4212-8CE5-4CD51EEA574F}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C6AD608D-93C8-4212-8CE5-4CD51EEA574F}" name="표12" displayName="표12" ref="A2:E7" totalsRowShown="0" headerRowDxfId="37">
+  <autoFilter ref="A2:E7" xr:uid="{C6AD608D-93C8-4212-8CE5-4CD51EEA574F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
     <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="6">
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{0C4F43A6-A7D1-4744-9F57-1599017C8F2F}" name="Column"/>
-    <tableColumn id="2" xr3:uid="{D6928E51-A7B6-475D-9760-A2907C79016A}" name="Data Type" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{59873623-3F04-4F20-A0A6-FD88D0DBF3BC}" name="Default"/>
-    <tableColumn id="4" xr3:uid="{C0901A66-7DC0-4D0F-ACD7-E7D5E59612BD}" name="PK"/>
-    <tableColumn id="5" xr3:uid="{365DA2C2-8432-46E6-877B-C2F869F5BB33}" name="NN" dataDxfId="69"/>
-    <tableColumn id="6" xr3:uid="{CD0440C7-8DC9-4002-9BF1-C7E222F14732}" name="Comment" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{D6928E51-A7B6-475D-9760-A2907C79016A}" name="Data Type" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{365DA2C2-8432-46E6-877B-C2F869F5BB33}" name="NN" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{CD0440C7-8DC9-4002-9BF1-C7E222F14732}" name="Comment" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{1924BA3E-2E3E-4620-B4A3-496C13AF16BA}" name="비고"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4345,294 +3762,242 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="13" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="27.125" customWidth="1"/>
-    <col min="7" max="7" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="27.125" customWidth="1"/>
+    <col min="5" max="5" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A1" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="62"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A2" s="27" t="s">
+    <row r="1" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A1" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" thickTop="1" thickBot="1">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="C2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="D2" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="27" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="E2" s="25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="33">
+        <v>73</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="33">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="33">
+      <c r="E4" s="19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="33">
       <c r="A5" s="15" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="B6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="D6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" ht="33">
+      <c r="A9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="33">
+      <c r="A10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:7" ht="33">
-      <c r="A9" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="33">
-      <c r="A10" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="9" t="s">
+      <c r="C11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="B12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="B14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="17"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G12" s="17"/>
-    </row>
-    <row r="13" spans="1:7" ht="33">
-      <c r="A13" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" s="17"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="16" t="s">
+      <c r="C14" s="10"/>
+      <c r="D14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="17"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="17"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
+      <c r="E15" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4659,123 +4024,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A1" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="37" t="s">
+      <c r="E2" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="39" t="s">
-        <v>103</v>
+      <c r="H2" s="35" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.25" thickTop="1">
       <c r="A3" s="14" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="H3" s="26"/>
+        <v>133</v>
+      </c>
+      <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="14" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="14" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="14" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
@@ -4784,114 +4149,114 @@
       <c r="E7" s="9"/>
       <c r="F7" s="10"/>
       <c r="G7" s="14" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="14" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="10"/>
       <c r="G8" s="14" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="14" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="14" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="13" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="10"/>
       <c r="G10" s="14" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="13" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="10"/>
       <c r="G11" s="14" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="41">
+      <c r="A12" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="37">
         <v>0</v>
       </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="H12" s="42"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H12" s="38"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
+      <c r="A13" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="78" t="s">
-        <v>165</v>
-      </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
+      <c r="A14" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
       <c r="H14" s="9"/>
     </row>
   </sheetData>
@@ -4925,84 +4290,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A1" s="64" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="37" t="s">
+      <c r="E2" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="39" t="s">
-        <v>103</v>
+      <c r="H2" s="35" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.25" thickTop="1">
       <c r="A3" s="14" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="14" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="H3" s="22"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="14" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="9"/>
       <c r="E4" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="H4" s="22"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="9" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>8</v>
@@ -5010,31 +4375,31 @@
       <c r="C5" s="9"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="9" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33">
       <c r="A6" s="9" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="12" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="13" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>8</v>
@@ -5044,13 +4409,13 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="14" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="H7" s="15"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="14" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>8</v>
@@ -5060,100 +4425,100 @@
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="14" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="14" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="H9" s="15"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="14" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="H10" s="15"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="14" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="10"/>
       <c r="G11" s="14" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="H11" s="15"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="14" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="10"/>
       <c r="G12" s="14" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="H12" s="15"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="14" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="14" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="H13" s="15"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="9" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
@@ -5162,47 +4527,47 @@
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="14" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="13" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="14" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="13" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
       <c r="G16" s="14" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="13" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C17" s="10">
         <v>0</v>
@@ -5211,44 +4576,44 @@
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="H17" s="32"/>
+        <v>170</v>
+      </c>
+      <c r="H17" s="28"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="77" t="s">
-        <v>129</v>
-      </c>
-      <c r="B18" s="77"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="32"/>
+      <c r="A18" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="28"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
+      <c r="A19" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
       <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="78" t="s">
-        <v>210</v>
-      </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
+      <c r="A20" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
       <c r="H20" s="9"/>
     </row>
   </sheetData>
@@ -5271,29 +4636,26 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="13" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="4.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-    </row>
-    <row r="2" spans="1:7">
+    <row r="1" spans="1:5">
+      <c r="A1" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5301,252 +4663,203 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="6" customFormat="1">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="6" customFormat="1">
+      <c r="A5" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="6" customFormat="1">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="6" customFormat="1">
-      <c r="A6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="E12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="33">
+        <v>70</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
         <v>29</v>
       </c>
-      <c r="F15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="69"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="69"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5562,320 +4875,202 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.375" customWidth="1"/>
-    <col min="9" max="9" width="36.25" customWidth="1"/>
+    <col min="3" max="3" width="4.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A1" s="64" t="s">
-        <v>244</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
-    </row>
-    <row r="2" spans="1:8" ht="17.25" thickTop="1">
-      <c r="A2" s="58" t="s">
+    <row r="1" spans="1:5" ht="18" thickTop="1" thickBot="1">
+      <c r="A1" s="60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="62"/>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" thickTop="1">
+      <c r="A2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="58" t="s">
+      <c r="C2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="D2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="58" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="E2" s="47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="H3" s="9"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="E4" s="49" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="49"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="49"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="H5" s="63"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="H6" s="63"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="H7" s="63"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:8" ht="33">
+      <c r="E10" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="13" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="10">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="13" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="55" t="s">
-        <v>231</v>
-      </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="16"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="55" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="16"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="G25" s="54"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="G26" s="52"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="G27" s="54"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="G28" s="53"/>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" s="46"/>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" s="44"/>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" s="46"/>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5887,423 +5082,182 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4.75" customWidth="1"/>
-    <col min="6" max="6" width="5.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="43" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5" customWidth="1"/>
-    <col min="9" max="9" width="36.25" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" thickTop="1" thickBot="1">
-      <c r="A1" s="64" t="s">
-        <v>256</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
-    </row>
-    <row r="2" spans="1:15" ht="18" thickTop="1" thickBot="1">
-      <c r="A2" s="39" t="s">
+    <row r="1" spans="1:5" ht="18" thickTop="1" thickBot="1">
+      <c r="A1" s="60" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="62"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" thickTop="1" thickBot="1">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="39" t="s">
+      <c r="C2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="D2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>260</v>
-      </c>
-      <c r="K2" s="39" t="s">
-        <v>261</v>
-      </c>
-      <c r="L2" s="39" t="s">
+      <c r="E2" s="35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickTop="1">
+      <c r="A3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="M2" s="39" t="s">
-        <v>263</v>
-      </c>
-      <c r="N2" s="39" t="s">
-        <v>264</v>
-      </c>
-      <c r="O2" s="39" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="17.25" thickTop="1">
-      <c r="A3" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="B3" s="31" t="s">
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-    </row>
-    <row r="12" spans="1:15" ht="33">
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="13" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="10">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9"/>
+        <v>26</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="E12" s="9"/>
-      <c r="F12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="67" t="s">
-        <v>254</v>
-      </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="69"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="69"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="67" t="s">
-        <v>255</v>
-      </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="69"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:H18"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6318,266 +5272,163 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="14.25" customWidth="1"/>
     <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="7" max="7" width="21.875" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="8.375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="73" t="s">
-        <v>313</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="46"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="44" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="68"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="44" t="s">
+      <c r="C2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="D2" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="E2" s="40" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="14" t="s">
-        <v>310</v>
+        <v>216</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="66" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" s="66" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="66"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="69" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="H3" s="21"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="30" t="s">
-        <v>311</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>308</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>315</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="14"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="9"/>
-      <c r="B10" s="11"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>26</v>
+      </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="81" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="81" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="82" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="9"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="14"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="9"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="14"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="17"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="14"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="17"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="14"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="17"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="B18" s="13" t="s">
+      <c r="D10" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H18" s="17"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" s="17"/>
+      <c r="E10" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6593,460 +5444,244 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="42.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.25" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.25" customWidth="1"/>
+    <col min="6" max="6" width="36.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="73" t="s">
-        <v>309</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="46"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="44" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="41"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="44" t="s">
+      <c r="C2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="D2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="44" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="E2" s="40" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4" s="66" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="72" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E6" s="66" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="E7" s="72"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A11" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="E11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A12" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" s="17"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="H3" s="21"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="14"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="H11" s="17"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="14" t="s">
-        <v>283</v>
+      <c r="E14" s="17"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="10">
-        <v>3</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="H16" s="17"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="H17" s="17"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="H18" s="17"/>
-    </row>
-    <row r="19" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="10">
-        <v>0</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="10">
-        <v>0</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="H20" s="17"/>
-    </row>
-    <row r="21" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="17"/>
-    </row>
-    <row r="22" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="17"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="17"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="B24" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" s="17"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="17"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="14"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="43" t="s">
-        <v>305</v>
-      </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="43"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" s="3"/>
+      <c r="E15" s="17"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7063,31 +5698,26 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4.75" customWidth="1"/>
-    <col min="6" max="6" width="5.5" customWidth="1"/>
-    <col min="7" max="7" width="30.5" customWidth="1"/>
+    <col min="3" max="3" width="5.5" customWidth="1"/>
+    <col min="4" max="4" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="73" t="s">
-        <v>300</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-    </row>
-    <row r="2" spans="1:8">
+    <row r="1" spans="1:5">
+      <c r="A1" s="56" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7095,260 +5725,155 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="14" t="s">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="9"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="37"/>
+      <c r="D10" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" s="9"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="9"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:8" ht="33">
-      <c r="A8" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="10">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="E10" s="38"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A11" s="74" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="76"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="70" t="s">
-        <v>301</v>
-      </c>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="72"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" s="5"/>
-      <c r="C14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="4"/>
+      <c r="E11" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7363,31 +5888,28 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" style="3" customWidth="1"/>
-    <col min="4" max="4" width="6.375" customWidth="1"/>
-    <col min="5" max="5" width="6.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="73" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    <row r="1" spans="1:5">
+      <c r="A1" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7395,88 +5917,88 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="3" customFormat="1">
-      <c r="A8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8" s="1"/>
-      <c r="F8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7503,144 +6025,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A1" s="64" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="37" t="s">
+      <c r="E2" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="39" t="s">
-        <v>103</v>
+      <c r="H2" s="35" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.25" thickTop="1">
       <c r="A3" s="14" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H3" s="26"/>
+        <v>97</v>
+      </c>
+      <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="14" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="9"/>
       <c r="E4" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
+        <v>100</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
       <c r="E6" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="10"/>
-      <c r="G6" s="36" t="s">
-        <v>138</v>
+      <c r="G6" s="32" t="s">
+        <v>101</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
+        <v>106</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="14" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>8</v>
@@ -7649,55 +6171,55 @@
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="14" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="14" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="14" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
@@ -7706,153 +6228,153 @@
       <c r="E11" s="9"/>
       <c r="F11" s="10"/>
       <c r="G11" s="14" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="14" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="10"/>
       <c r="G12" s="14" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="14" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="14" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="13" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="14" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="13" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="14" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="B16" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="41">
+      <c r="A16" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="37">
         <v>0</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="42"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="38"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="69"/>
+      <c r="A17" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="59"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="69"/>
+      <c r="A18" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="59"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="67" t="s">
-        <v>148</v>
-      </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="69"/>
+      <c r="A19" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="59"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="67" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="68"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="69"/>
+      <c r="A20" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="59"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="72"/>
+      <c r="A21" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="6">
